--- a/fix/testspages-link/ig/ValueSet-sas-valueset-appointmentparticipanttype.xlsx
+++ b/fix/testspages-link/ig/ValueSet-sas-valueset-appointmentparticipanttype.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T08:33:06+00:00</t>
+    <t>2026-07-17T08:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/testspages-link/ig/ValueSet-sas-valueset-appointmentparticipanttype.xlsx
+++ b/fix/testspages-link/ig/ValueSet-sas-valueset-appointmentparticipanttype.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T08:35:39+00:00</t>
+    <t>2026-07-17T08:54:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
